--- a/Tax free/Tax free armado/Tax free_2026-08.xlsx
+++ b/Tax free/Tax free armado/Tax free_2026-08.xlsx
@@ -980,7 +980,7 @@
     <t xml:space="preserve">45-1643</t>
   </si>
   <si>
-    <t xml:space="preserve">Guemes</t>
+    <t xml:space="preserve">Güemes</t>
   </si>
   <si>
     <t xml:space="preserve">18:22:42</t>
@@ -2099,10 +2099,10 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>118.93</v>
+        <v>118930</v>
       </c>
       <c r="J2" t="n">
-        <v>15.4609</v>
+        <v>15460.9</v>
       </c>
     </row>
     <row r="3">
@@ -2131,10 +2131,10 @@
         <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>122.97</v>
+        <v>122970</v>
       </c>
       <c r="J3" t="n">
-        <v>15.9861</v>
+        <v>15986.1</v>
       </c>
     </row>
     <row r="4">
@@ -2163,10 +2163,10 @@
         <v>22</v>
       </c>
       <c r="I4" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J4" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="5">
@@ -2195,10 +2195,10 @@
         <v>24</v>
       </c>
       <c r="I5" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J5" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="6">
@@ -2227,10 +2227,10 @@
         <v>26</v>
       </c>
       <c r="I6" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J6" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="7">
@@ -2259,10 +2259,10 @@
         <v>29</v>
       </c>
       <c r="I7" t="n">
-        <v>139.98</v>
+        <v>139980</v>
       </c>
       <c r="J7" t="n">
-        <v>18.1974</v>
+        <v>18197.4</v>
       </c>
     </row>
     <row r="8">
@@ -2291,10 +2291,10 @@
         <v>31</v>
       </c>
       <c r="I8" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J8" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="9">
@@ -2323,10 +2323,10 @@
         <v>35</v>
       </c>
       <c r="I9" t="n">
-        <v>199.99</v>
+        <v>199990</v>
       </c>
       <c r="J9" t="n">
-        <v>25.9987</v>
+        <v>25998.7</v>
       </c>
     </row>
     <row r="10">
@@ -2355,10 +2355,10 @@
         <v>37</v>
       </c>
       <c r="I10" t="n">
-        <v>39.99</v>
+        <v>39990</v>
       </c>
       <c r="J10" t="n">
-        <v>5.1987</v>
+        <v>5198.7</v>
       </c>
     </row>
     <row r="11">
@@ -2387,10 +2387,10 @@
         <v>41</v>
       </c>
       <c r="I11" t="n">
-        <v>269.99</v>
+        <v>269990</v>
       </c>
       <c r="J11" t="n">
-        <v>35.0987</v>
+        <v>35098.7</v>
       </c>
     </row>
     <row r="12">
@@ -2419,10 +2419,10 @@
         <v>44</v>
       </c>
       <c r="I12" t="n">
-        <v>255.99</v>
+        <v>255990</v>
       </c>
       <c r="J12" t="n">
-        <v>33.2787</v>
+        <v>33278.7</v>
       </c>
     </row>
     <row r="13">
@@ -2451,10 +2451,10 @@
         <v>47</v>
       </c>
       <c r="I13" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J13" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="14">
@@ -2483,10 +2483,10 @@
         <v>50</v>
       </c>
       <c r="I14" t="n">
-        <v>38.97</v>
+        <v>38970</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0661</v>
+        <v>5066.1</v>
       </c>
     </row>
     <row r="15">
@@ -2515,10 +2515,10 @@
         <v>52</v>
       </c>
       <c r="I15" t="n">
-        <v>12.99</v>
+        <v>12990</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6887</v>
+        <v>1688.7</v>
       </c>
     </row>
     <row r="16">
@@ -2547,10 +2547,10 @@
         <v>54</v>
       </c>
       <c r="I16" t="n">
-        <v>14.99</v>
+        <v>14990</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9487</v>
+        <v>1948.7</v>
       </c>
     </row>
     <row r="17">
@@ -2579,10 +2579,10 @@
         <v>56</v>
       </c>
       <c r="I17" t="n">
-        <v>299.9</v>
+        <v>299900</v>
       </c>
       <c r="J17" t="n">
-        <v>38.987</v>
+        <v>38987</v>
       </c>
     </row>
     <row r="18">
@@ -2611,10 +2611,10 @@
         <v>59</v>
       </c>
       <c r="I18" t="n">
-        <v>69.99</v>
+        <v>69990</v>
       </c>
       <c r="J18" t="n">
-        <v>9.0987</v>
+        <v>9098.7</v>
       </c>
     </row>
     <row r="19">
@@ -2643,10 +2643,10 @@
         <v>61</v>
       </c>
       <c r="I19" t="n">
-        <v>44.97</v>
+        <v>44970</v>
       </c>
       <c r="J19" t="n">
-        <v>5.8461</v>
+        <v>5846.1</v>
       </c>
     </row>
     <row r="20">
@@ -2675,10 +2675,10 @@
         <v>63</v>
       </c>
       <c r="I20" t="n">
-        <v>14.99</v>
+        <v>14990</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9487</v>
+        <v>1948.7</v>
       </c>
     </row>
     <row r="21">
@@ -2707,10 +2707,10 @@
         <v>65</v>
       </c>
       <c r="I21" t="n">
-        <v>189.99</v>
+        <v>189990</v>
       </c>
       <c r="J21" t="n">
-        <v>24.6987</v>
+        <v>24698.7</v>
       </c>
     </row>
     <row r="22">
@@ -2739,10 +2739,10 @@
         <v>67</v>
       </c>
       <c r="I22" t="n">
-        <v>109.98</v>
+        <v>109980</v>
       </c>
       <c r="J22" t="n">
-        <v>14.2974</v>
+        <v>14297.4</v>
       </c>
     </row>
     <row r="23">
@@ -2771,10 +2771,10 @@
         <v>71</v>
       </c>
       <c r="I23" t="n">
-        <v>89.99</v>
+        <v>89990</v>
       </c>
       <c r="J23" t="n">
-        <v>11.6987</v>
+        <v>11698.7</v>
       </c>
     </row>
     <row r="24">
@@ -2803,10 +2803,10 @@
         <v>74</v>
       </c>
       <c r="I24" t="n">
-        <v>704.628</v>
+        <v>704628</v>
       </c>
       <c r="J24" t="n">
-        <v>98.64792</v>
+        <v>98647.92</v>
       </c>
     </row>
     <row r="25">
@@ -2835,10 +2835,10 @@
         <v>77</v>
       </c>
       <c r="I25" t="n">
-        <v>125.97</v>
+        <v>125970</v>
       </c>
       <c r="J25" t="n">
-        <v>16.3761</v>
+        <v>16376.1</v>
       </c>
     </row>
     <row r="26">
@@ -2867,10 +2867,10 @@
         <v>79</v>
       </c>
       <c r="I26" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J26" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="27">
@@ -2899,10 +2899,10 @@
         <v>81</v>
       </c>
       <c r="I27" t="n">
-        <v>169.99</v>
+        <v>169990</v>
       </c>
       <c r="J27" t="n">
-        <v>22.0987</v>
+        <v>22098.7</v>
       </c>
     </row>
     <row r="28">
@@ -2931,10 +2931,10 @@
         <v>84</v>
       </c>
       <c r="I28" t="n">
-        <v>3.338</v>
+        <v>3338</v>
       </c>
       <c r="J28" t="n">
-        <v>43394</v>
+        <v>433.94</v>
       </c>
     </row>
     <row r="29">
@@ -2963,10 +2963,10 @@
         <v>86</v>
       </c>
       <c r="I29" t="n">
-        <v>789.97</v>
+        <v>789970</v>
       </c>
       <c r="J29" t="n">
-        <v>110.5958</v>
+        <v>110595.8</v>
       </c>
     </row>
     <row r="30">
@@ -2995,10 +2995,10 @@
         <v>89</v>
       </c>
       <c r="I30" t="n">
-        <v>185.95</v>
+        <v>185950</v>
       </c>
       <c r="J30" t="n">
-        <v>24.1735</v>
+        <v>24173.5</v>
       </c>
     </row>
     <row r="31">
@@ -3027,10 +3027,10 @@
         <v>91</v>
       </c>
       <c r="I31" t="n">
-        <v>209.98</v>
+        <v>209980</v>
       </c>
       <c r="J31" t="n">
-        <v>27.2974</v>
+        <v>27297.4</v>
       </c>
     </row>
     <row r="32">
@@ -3059,10 +3059,10 @@
         <v>93</v>
       </c>
       <c r="I32" t="n">
-        <v>189.99</v>
+        <v>189990</v>
       </c>
       <c r="J32" t="n">
-        <v>24.6987</v>
+        <v>24698.7</v>
       </c>
     </row>
     <row r="33">
@@ -3091,10 +3091,10 @@
         <v>95</v>
       </c>
       <c r="I33" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J33" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="34">
@@ -3123,10 +3123,10 @@
         <v>98</v>
       </c>
       <c r="I34" t="n">
-        <v>134.98</v>
+        <v>134980</v>
       </c>
       <c r="J34" t="n">
-        <v>17.5474</v>
+        <v>17547.4</v>
       </c>
     </row>
     <row r="35">
@@ -3155,10 +3155,10 @@
         <v>101</v>
       </c>
       <c r="I35" t="n">
-        <v>69.99</v>
+        <v>69990</v>
       </c>
       <c r="J35" t="n">
-        <v>9.0987</v>
+        <v>9098.7</v>
       </c>
     </row>
     <row r="36">
@@ -3187,10 +3187,10 @@
         <v>103</v>
       </c>
       <c r="I36" t="n">
-        <v>79.99</v>
+        <v>79990</v>
       </c>
       <c r="J36" t="n">
-        <v>10.3987</v>
+        <v>10398.7</v>
       </c>
     </row>
     <row r="37">
@@ -3219,10 +3219,10 @@
         <v>106</v>
       </c>
       <c r="I37" t="n">
-        <v>169.99</v>
+        <v>169990</v>
       </c>
       <c r="J37" t="n">
-        <v>22.0987</v>
+        <v>22098.7</v>
       </c>
     </row>
     <row r="38">
@@ -3251,10 +3251,10 @@
         <v>108</v>
       </c>
       <c r="I38" t="n">
-        <v>84.99</v>
+        <v>84990</v>
       </c>
       <c r="J38" t="n">
-        <v>11.0487</v>
+        <v>11048.7</v>
       </c>
     </row>
     <row r="39">
@@ -3283,10 +3283,10 @@
         <v>111</v>
       </c>
       <c r="I39" t="n">
-        <v>24.99</v>
+        <v>24990</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2487</v>
+        <v>3248.7</v>
       </c>
     </row>
     <row r="40">
@@ -3315,10 +3315,10 @@
         <v>113</v>
       </c>
       <c r="I40" t="n">
-        <v>79.99</v>
+        <v>79990</v>
       </c>
       <c r="J40" t="n">
-        <v>10.3987</v>
+        <v>10398.7</v>
       </c>
     </row>
     <row r="41">
@@ -3347,10 +3347,10 @@
         <v>115</v>
       </c>
       <c r="I41" t="n">
-        <v>119.97</v>
+        <v>119970</v>
       </c>
       <c r="J41" t="n">
-        <v>15.5961</v>
+        <v>15596.1</v>
       </c>
     </row>
     <row r="42">
@@ -3379,10 +3379,10 @@
         <v>117</v>
       </c>
       <c r="I42" t="n">
-        <v>105.95</v>
+        <v>105950</v>
       </c>
       <c r="J42" t="n">
-        <v>13.7735</v>
+        <v>13773.5</v>
       </c>
     </row>
     <row r="43">
@@ -3411,10 +3411,10 @@
         <v>120</v>
       </c>
       <c r="I43" t="n">
-        <v>159.99</v>
+        <v>159990</v>
       </c>
       <c r="J43" t="n">
-        <v>20.7987</v>
+        <v>20798.7</v>
       </c>
     </row>
     <row r="44">
@@ -3443,10 +3443,10 @@
         <v>122</v>
       </c>
       <c r="I44" t="n">
-        <v>56.98</v>
+        <v>56980</v>
       </c>
       <c r="J44" t="n">
-        <v>7.4074</v>
+        <v>7407.4</v>
       </c>
     </row>
     <row r="45">
@@ -3475,10 +3475,10 @@
         <v>124</v>
       </c>
       <c r="I45" t="n">
-        <v>344.98</v>
+        <v>344980</v>
       </c>
       <c r="J45" t="n">
-        <v>44.8474</v>
+        <v>44847.4</v>
       </c>
     </row>
     <row r="46">
@@ -3507,10 +3507,10 @@
         <v>126</v>
       </c>
       <c r="I46" t="n">
-        <v>313.96</v>
+        <v>313960</v>
       </c>
       <c r="J46" t="n">
-        <v>40.8148</v>
+        <v>40814.8</v>
       </c>
     </row>
     <row r="47">
@@ -3539,10 +3539,10 @@
         <v>128</v>
       </c>
       <c r="I47" t="n">
-        <v>239.9</v>
+        <v>239900</v>
       </c>
       <c r="J47" t="n">
-        <v>31.187</v>
+        <v>31187</v>
       </c>
     </row>
     <row r="48">
@@ -3571,10 +3571,10 @@
         <v>130</v>
       </c>
       <c r="I48" t="n">
-        <v>159.97</v>
+        <v>159970</v>
       </c>
       <c r="J48" t="n">
-        <v>20.7961</v>
+        <v>20796.1</v>
       </c>
     </row>
     <row r="49">
@@ -3603,10 +3603,10 @@
         <v>132</v>
       </c>
       <c r="I49" t="n">
-        <v>329.98</v>
+        <v>329980</v>
       </c>
       <c r="J49" t="n">
-        <v>42.8974</v>
+        <v>42897.4</v>
       </c>
     </row>
     <row r="50">
@@ -3635,10 +3635,10 @@
         <v>134</v>
       </c>
       <c r="I50" t="n">
-        <v>79.99</v>
+        <v>79990</v>
       </c>
       <c r="J50" t="n">
-        <v>10.3987</v>
+        <v>10398.7</v>
       </c>
     </row>
     <row r="51">
@@ -3667,10 +3667,10 @@
         <v>136</v>
       </c>
       <c r="I51" t="n">
-        <v>189.99</v>
+        <v>189990</v>
       </c>
       <c r="J51" t="n">
-        <v>24.6987</v>
+        <v>24698.7</v>
       </c>
     </row>
     <row r="52">
@@ -3699,10 +3699,10 @@
         <v>138</v>
       </c>
       <c r="I52" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J52" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="53">
@@ -3731,10 +3731,10 @@
         <v>140</v>
       </c>
       <c r="I53" t="n">
-        <v>259.96</v>
+        <v>259960</v>
       </c>
       <c r="J53" t="n">
-        <v>33.7948</v>
+        <v>33794.8</v>
       </c>
     </row>
     <row r="54">
@@ -3763,10 +3763,10 @@
         <v>142</v>
       </c>
       <c r="I54" t="n">
-        <v>24.98</v>
+        <v>24980</v>
       </c>
       <c r="J54" t="n">
-        <v>3.2474</v>
+        <v>3247.4</v>
       </c>
     </row>
     <row r="55">
@@ -3795,10 +3795,10 @@
         <v>144</v>
       </c>
       <c r="I55" t="n">
-        <v>145.96</v>
+        <v>145960</v>
       </c>
       <c r="J55" t="n">
-        <v>18.9748</v>
+        <v>18974.8</v>
       </c>
     </row>
     <row r="56">
@@ -3827,10 +3827,10 @@
         <v>146</v>
       </c>
       <c r="I56" t="n">
-        <v>34.99</v>
+        <v>34990</v>
       </c>
       <c r="J56" t="n">
-        <v>4.5487</v>
+        <v>4548.7</v>
       </c>
     </row>
     <row r="57">
@@ -3859,10 +3859,10 @@
         <v>148</v>
       </c>
       <c r="I57" t="n">
-        <v>325.98</v>
+        <v>325980</v>
       </c>
       <c r="J57" t="n">
-        <v>42.3774</v>
+        <v>42377.4</v>
       </c>
     </row>
     <row r="58">
@@ -3891,10 +3891,10 @@
         <v>150</v>
       </c>
       <c r="I58" t="n">
-        <v>299.99</v>
+        <v>299990</v>
       </c>
       <c r="J58" t="n">
-        <v>38.9987</v>
+        <v>38998.7</v>
       </c>
     </row>
     <row r="59">
@@ -3923,10 +3923,10 @@
         <v>152</v>
       </c>
       <c r="I59" t="n">
-        <v>29.99</v>
+        <v>29990</v>
       </c>
       <c r="J59" t="n">
-        <v>3.8987</v>
+        <v>3898.7</v>
       </c>
     </row>
     <row r="60">
@@ -3955,10 +3955,10 @@
         <v>155</v>
       </c>
       <c r="I60" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J60" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="61">
@@ -3987,10 +3987,10 @@
         <v>157</v>
       </c>
       <c r="I61" t="n">
-        <v>494.97</v>
+        <v>494970</v>
       </c>
       <c r="J61" t="n">
-        <v>69.2958</v>
+        <v>69295.8</v>
       </c>
     </row>
     <row r="62">
@@ -4019,10 +4019,10 @@
         <v>159</v>
       </c>
       <c r="I62" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J62" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="63">
@@ -4051,10 +4051,10 @@
         <v>161</v>
       </c>
       <c r="I63" t="n">
-        <v>199.98</v>
+        <v>199980</v>
       </c>
       <c r="J63" t="n">
-        <v>25.9974</v>
+        <v>25997.4</v>
       </c>
     </row>
     <row r="64">
@@ -4083,10 +4083,10 @@
         <v>163</v>
       </c>
       <c r="I64" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J64" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="65">
@@ -4115,10 +4115,10 @@
         <v>165</v>
       </c>
       <c r="I65" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J65" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="66">
@@ -4147,10 +4147,10 @@
         <v>167</v>
       </c>
       <c r="I66" t="n">
-        <v>239.98</v>
+        <v>239980</v>
       </c>
       <c r="J66" t="n">
-        <v>31.1974</v>
+        <v>31197.4</v>
       </c>
     </row>
     <row r="67">
@@ -4179,10 +4179,10 @@
         <v>169</v>
       </c>
       <c r="I67" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J67" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="68">
@@ -4211,10 +4211,10 @@
         <v>171</v>
       </c>
       <c r="I68" t="n">
-        <v>79.99</v>
+        <v>79990</v>
       </c>
       <c r="J68" t="n">
-        <v>10.3987</v>
+        <v>10398.7</v>
       </c>
     </row>
     <row r="69">
@@ -4243,10 +4243,10 @@
         <v>173</v>
       </c>
       <c r="I69" t="n">
-        <v>173.96</v>
+        <v>173960</v>
       </c>
       <c r="J69" t="n">
-        <v>22.6148</v>
+        <v>22614.8</v>
       </c>
     </row>
     <row r="70">
@@ -4275,10 +4275,10 @@
         <v>175</v>
       </c>
       <c r="I70" t="n">
-        <v>88.97</v>
+        <v>88970</v>
       </c>
       <c r="J70" t="n">
-        <v>11.5661</v>
+        <v>11566.1</v>
       </c>
     </row>
     <row r="71">
@@ -4307,10 +4307,10 @@
         <v>177</v>
       </c>
       <c r="I71" t="n">
-        <v>166.95</v>
+        <v>166950</v>
       </c>
       <c r="J71" t="n">
-        <v>21.7035</v>
+        <v>21703.5</v>
       </c>
     </row>
     <row r="72">
@@ -4339,10 +4339,10 @@
         <v>180</v>
       </c>
       <c r="I72" t="n">
-        <v>74.99</v>
+        <v>74990</v>
       </c>
       <c r="J72" t="n">
-        <v>9.7487</v>
+        <v>9748.7</v>
       </c>
     </row>
     <row r="73">
@@ -4371,10 +4371,10 @@
         <v>183</v>
       </c>
       <c r="I73" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J73" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="74">
@@ -4403,10 +4403,10 @@
         <v>185</v>
       </c>
       <c r="I74" t="n">
-        <v>65.99</v>
+        <v>65990</v>
       </c>
       <c r="J74" t="n">
-        <v>8.5787</v>
+        <v>8578.7</v>
       </c>
     </row>
     <row r="75">
@@ -4435,10 +4435,10 @@
         <v>187</v>
       </c>
       <c r="I75" t="n">
-        <v>239.98</v>
+        <v>239980</v>
       </c>
       <c r="J75" t="n">
-        <v>31.1974</v>
+        <v>31197.4</v>
       </c>
     </row>
     <row r="76">
@@ -4467,10 +4467,10 @@
         <v>189</v>
       </c>
       <c r="I76" t="n">
-        <v>119.98</v>
+        <v>119980</v>
       </c>
       <c r="J76" t="n">
-        <v>15.5974</v>
+        <v>15597.4</v>
       </c>
     </row>
     <row r="77">
@@ -4499,10 +4499,10 @@
         <v>191</v>
       </c>
       <c r="I77" t="n">
-        <v>109.98</v>
+        <v>109980</v>
       </c>
       <c r="J77" t="n">
-        <v>14.2974</v>
+        <v>14297.4</v>
       </c>
     </row>
     <row r="78">
@@ -4531,10 +4531,10 @@
         <v>193</v>
       </c>
       <c r="I78" t="n">
-        <v>33.98</v>
+        <v>33980</v>
       </c>
       <c r="J78" t="n">
-        <v>4.4174</v>
+        <v>4417.4</v>
       </c>
     </row>
     <row r="79">
@@ -4563,10 +4563,10 @@
         <v>195</v>
       </c>
       <c r="I79" t="n">
-        <v>50.97</v>
+        <v>50970</v>
       </c>
       <c r="J79" t="n">
-        <v>6.6261</v>
+        <v>6626.1</v>
       </c>
     </row>
     <row r="80">
@@ -4595,10 +4595,10 @@
         <v>197</v>
       </c>
       <c r="I80" t="n">
-        <v>35.98</v>
+        <v>35980</v>
       </c>
       <c r="J80" t="n">
-        <v>4.6774</v>
+        <v>4677.4</v>
       </c>
     </row>
     <row r="81">
@@ -4627,10 +4627,10 @@
         <v>200</v>
       </c>
       <c r="I81" t="n">
-        <v>118.93</v>
+        <v>118930</v>
       </c>
       <c r="J81" t="n">
-        <v>15.4609</v>
+        <v>15460.9</v>
       </c>
     </row>
     <row r="82">
@@ -4659,10 +4659,10 @@
         <v>202</v>
       </c>
       <c r="I82" t="n">
-        <v>509.92</v>
+        <v>509920</v>
       </c>
       <c r="J82" t="n">
-        <v>71.3888</v>
+        <v>71388.8</v>
       </c>
     </row>
     <row r="83">
@@ -4691,10 +4691,10 @@
         <v>204</v>
       </c>
       <c r="I83" t="n">
-        <v>63.95</v>
+        <v>63950</v>
       </c>
       <c r="J83" t="n">
-        <v>8.3135</v>
+        <v>8313.5</v>
       </c>
     </row>
     <row r="84">
@@ -4723,10 +4723,10 @@
         <v>206</v>
       </c>
       <c r="I84" t="n">
-        <v>109.98</v>
+        <v>109980</v>
       </c>
       <c r="J84" t="n">
-        <v>14.2974</v>
+        <v>14297.4</v>
       </c>
     </row>
     <row r="85">
@@ -4755,10 +4755,10 @@
         <v>208</v>
       </c>
       <c r="I85" t="n">
-        <v>54.99</v>
+        <v>54990</v>
       </c>
       <c r="J85" t="n">
-        <v>7.1487</v>
+        <v>7148.7</v>
       </c>
     </row>
     <row r="86">
@@ -4787,10 +4787,10 @@
         <v>210</v>
       </c>
       <c r="I86" t="n">
-        <v>152.91</v>
+        <v>152910</v>
       </c>
       <c r="J86" t="n">
-        <v>19.8783</v>
+        <v>19878.3</v>
       </c>
     </row>
     <row r="87">
@@ -4819,10 +4819,10 @@
         <v>213</v>
       </c>
       <c r="I87" t="n">
-        <v>69.99</v>
+        <v>69990</v>
       </c>
       <c r="J87" t="n">
-        <v>9.0987</v>
+        <v>9098.7</v>
       </c>
     </row>
     <row r="88">
@@ -4851,10 +4851,10 @@
         <v>216</v>
       </c>
       <c r="I88" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J88" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="89">
@@ -4883,10 +4883,10 @@
         <v>218</v>
       </c>
       <c r="I89" t="n">
-        <v>46.97</v>
+        <v>46970</v>
       </c>
       <c r="J89" t="n">
-        <v>6.1061</v>
+        <v>6106.1</v>
       </c>
     </row>
     <row r="90">
@@ -4915,10 +4915,10 @@
         <v>220</v>
       </c>
       <c r="I90" t="n">
-        <v>112.99</v>
+        <v>112990</v>
       </c>
       <c r="J90" t="n">
-        <v>14.6887</v>
+        <v>14688.7</v>
       </c>
     </row>
     <row r="91">
@@ -4947,10 +4947,10 @@
         <v>222</v>
       </c>
       <c r="I91" t="n">
-        <v>38.98</v>
+        <v>38980</v>
       </c>
       <c r="J91" t="n">
-        <v>5.0674</v>
+        <v>5067.4</v>
       </c>
     </row>
     <row r="92">
@@ -4979,10 +4979,10 @@
         <v>224</v>
       </c>
       <c r="I92" t="n">
-        <v>74.99</v>
+        <v>74990</v>
       </c>
       <c r="J92" t="n">
-        <v>9.7487</v>
+        <v>9748.7</v>
       </c>
     </row>
     <row r="93">
@@ -5011,10 +5011,10 @@
         <v>226</v>
       </c>
       <c r="I93" t="n">
-        <v>119.98</v>
+        <v>119980</v>
       </c>
       <c r="J93" t="n">
-        <v>15.5974</v>
+        <v>15597.4</v>
       </c>
     </row>
     <row r="94">
@@ -5043,10 +5043,10 @@
         <v>228</v>
       </c>
       <c r="I94" t="n">
-        <v>149.96</v>
+        <v>149960</v>
       </c>
       <c r="J94" t="n">
-        <v>19.4948</v>
+        <v>19494.8</v>
       </c>
     </row>
     <row r="95">
@@ -5075,10 +5075,10 @@
         <v>231</v>
       </c>
       <c r="I95" t="n">
-        <v>104.99</v>
+        <v>104990</v>
       </c>
       <c r="J95" t="n">
-        <v>13.6487</v>
+        <v>13648.7</v>
       </c>
     </row>
     <row r="96">
@@ -5107,10 +5107,10 @@
         <v>233</v>
       </c>
       <c r="I96" t="n">
-        <v>129.99</v>
+        <v>129990</v>
       </c>
       <c r="J96" t="n">
-        <v>16.8987</v>
+        <v>16898.7</v>
       </c>
     </row>
     <row r="97">
@@ -5139,10 +5139,10 @@
         <v>235</v>
       </c>
       <c r="I97" t="n">
-        <v>69.98</v>
+        <v>69980</v>
       </c>
       <c r="J97" t="n">
-        <v>9.0974</v>
+        <v>9097.4</v>
       </c>
     </row>
     <row r="98">
@@ -5171,10 +5171,10 @@
         <v>237</v>
       </c>
       <c r="I98" t="n">
-        <v>59.99</v>
+        <v>59990</v>
       </c>
       <c r="J98" t="n">
-        <v>7.7987</v>
+        <v>7798.7</v>
       </c>
     </row>
     <row r="99">
@@ -5203,10 +5203,10 @@
         <v>239</v>
       </c>
       <c r="I99" t="n">
-        <v>299.98</v>
+        <v>299980</v>
       </c>
       <c r="J99" t="n">
-        <v>38.9974</v>
+        <v>38997.4</v>
       </c>
     </row>
     <row r="100">
@@ -5235,10 +5235,10 @@
         <v>241</v>
       </c>
       <c r="I100" t="n">
-        <v>16.99</v>
+        <v>16990</v>
       </c>
       <c r="J100" t="n">
-        <v>2.2087</v>
+        <v>2208.7</v>
       </c>
     </row>
     <row r="101">
@@ -5267,10 +5267,10 @@
         <v>243</v>
       </c>
       <c r="I101" t="n">
-        <v>16.99</v>
+        <v>16990</v>
       </c>
       <c r="J101" t="n">
-        <v>2.2087</v>
+        <v>2208.7</v>
       </c>
     </row>
     <row r="102">
@@ -5299,10 +5299,10 @@
         <v>245</v>
       </c>
       <c r="I102" t="n">
-        <v>159.99</v>
+        <v>159990</v>
       </c>
       <c r="J102" t="n">
-        <v>20.7987</v>
+        <v>20798.7</v>
       </c>
     </row>
     <row r="103">
@@ -5331,10 +5331,10 @@
         <v>247</v>
       </c>
       <c r="I103" t="n">
-        <v>164.94</v>
+        <v>164940</v>
       </c>
       <c r="J103" t="n">
-        <v>21.4422</v>
+        <v>21442.2</v>
       </c>
     </row>
     <row r="104">
@@ -5363,10 +5363,10 @@
         <v>249</v>
       </c>
       <c r="I104" t="n">
-        <v>109.97</v>
+        <v>109970</v>
       </c>
       <c r="J104" t="n">
-        <v>14.2961</v>
+        <v>14296.1</v>
       </c>
     </row>
     <row r="105">
@@ -5395,10 +5395,10 @@
         <v>251</v>
       </c>
       <c r="I105" t="n">
-        <v>66.98</v>
+        <v>66980</v>
       </c>
       <c r="J105" t="n">
-        <v>8.7074</v>
+        <v>8707.4</v>
       </c>
     </row>
     <row r="106">
@@ -5427,10 +5427,10 @@
         <v>253</v>
       </c>
       <c r="I106" t="n">
-        <v>16.99</v>
+        <v>16990</v>
       </c>
       <c r="J106" t="n">
-        <v>2.2087</v>
+        <v>2208.7</v>
       </c>
     </row>
     <row r="107">
@@ -5459,10 +5459,10 @@
         <v>255</v>
       </c>
       <c r="I107" t="n">
-        <v>879.98</v>
+        <v>879980</v>
       </c>
       <c r="J107" t="n">
-        <v>123.1972</v>
+        <v>123197.2</v>
       </c>
     </row>
     <row r="108">
@@ -5491,10 +5491,10 @@
         <v>258</v>
       </c>
       <c r="I108" t="n">
-        <v>16.99</v>
+        <v>16990</v>
       </c>
       <c r="J108" t="n">
-        <v>2.2087</v>
+        <v>2208.7</v>
       </c>
     </row>
     <row r="109">
@@ -5523,10 +5523,10 @@
         <v>260</v>
       </c>
       <c r="I109" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J109" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="110">
@@ -5555,10 +5555,10 @@
         <v>262</v>
       </c>
       <c r="I110" t="n">
-        <v>279.97</v>
+        <v>279970</v>
       </c>
       <c r="J110" t="n">
-        <v>36.3961</v>
+        <v>36396.1</v>
       </c>
     </row>
     <row r="111">
@@ -5587,10 +5587,10 @@
         <v>264</v>
       </c>
       <c r="I111" t="n">
-        <v>369.97</v>
+        <v>369970</v>
       </c>
       <c r="J111" t="n">
-        <v>48.0961</v>
+        <v>48096.1</v>
       </c>
     </row>
     <row r="112">
@@ -5619,10 +5619,10 @@
         <v>266</v>
       </c>
       <c r="I112" t="n">
-        <v>55.99</v>
+        <v>55990</v>
       </c>
       <c r="J112" t="n">
-        <v>7.2787</v>
+        <v>7278.7</v>
       </c>
     </row>
     <row r="113">
@@ -5651,10 +5651,10 @@
         <v>269</v>
       </c>
       <c r="I113" t="n">
-        <v>59.98</v>
+        <v>59980</v>
       </c>
       <c r="J113" t="n">
-        <v>7.7974</v>
+        <v>7797.4</v>
       </c>
     </row>
     <row r="114">
@@ -5683,10 +5683,10 @@
         <v>271</v>
       </c>
       <c r="I114" t="n">
-        <v>132.98</v>
+        <v>132980</v>
       </c>
       <c r="J114" t="n">
-        <v>17.2874</v>
+        <v>17287.4</v>
       </c>
     </row>
     <row r="115">
@@ -5715,10 +5715,10 @@
         <v>273</v>
       </c>
       <c r="I115" t="n">
-        <v>319.98</v>
+        <v>319980</v>
       </c>
       <c r="J115" t="n">
-        <v>41.5974</v>
+        <v>41597.4</v>
       </c>
     </row>
     <row r="116">
@@ -5747,10 +5747,10 @@
         <v>275</v>
       </c>
       <c r="I116" t="n">
-        <v>296.93</v>
+        <v>296930</v>
       </c>
       <c r="J116" t="n">
-        <v>38.6009</v>
+        <v>38600.9</v>
       </c>
     </row>
     <row r="117">
@@ -5779,10 +5779,10 @@
         <v>277</v>
       </c>
       <c r="I117" t="n">
-        <v>64.96</v>
+        <v>64960</v>
       </c>
       <c r="J117" t="n">
-        <v>8.4448</v>
+        <v>8444.8</v>
       </c>
     </row>
     <row r="118">
@@ -5811,10 +5811,10 @@
         <v>280</v>
       </c>
       <c r="I118" t="n">
-        <v>24.99</v>
+        <v>24990</v>
       </c>
       <c r="J118" t="n">
-        <v>3.2487</v>
+        <v>3248.7</v>
       </c>
     </row>
     <row r="119">
@@ -5843,10 +5843,10 @@
         <v>282</v>
       </c>
       <c r="I119" t="n">
-        <v>249.98</v>
+        <v>249980</v>
       </c>
       <c r="J119" t="n">
-        <v>32.4974</v>
+        <v>32497.4</v>
       </c>
     </row>
     <row r="120">
@@ -5875,10 +5875,10 @@
         <v>284</v>
       </c>
       <c r="I120" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J120" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="121">
@@ -5907,10 +5907,10 @@
         <v>286</v>
       </c>
       <c r="I121" t="n">
-        <v>159.99</v>
+        <v>159990</v>
       </c>
       <c r="J121" t="n">
-        <v>20.7987</v>
+        <v>20798.7</v>
       </c>
     </row>
     <row r="122">
@@ -5939,10 +5939,10 @@
         <v>288</v>
       </c>
       <c r="I122" t="n">
-        <v>729.95</v>
+        <v>729950</v>
       </c>
       <c r="J122" t="n">
-        <v>102.193</v>
+        <v>102193</v>
       </c>
     </row>
     <row r="123">
@@ -5971,10 +5971,10 @@
         <v>290</v>
       </c>
       <c r="I123" t="n">
-        <v>319.98</v>
+        <v>319980</v>
       </c>
       <c r="J123" t="n">
-        <v>41.5974</v>
+        <v>41597.4</v>
       </c>
     </row>
     <row r="124">
@@ -6003,10 +6003,10 @@
         <v>292</v>
       </c>
       <c r="I124" t="n">
-        <v>29.99</v>
+        <v>29990</v>
       </c>
       <c r="J124" t="n">
-        <v>3.8987</v>
+        <v>3898.7</v>
       </c>
     </row>
     <row r="125">
@@ -6035,10 +6035,10 @@
         <v>294</v>
       </c>
       <c r="I125" t="n">
-        <v>104.98</v>
+        <v>104980</v>
       </c>
       <c r="J125" t="n">
-        <v>13.6474</v>
+        <v>13647.4</v>
       </c>
     </row>
     <row r="126">
@@ -6067,10 +6067,10 @@
         <v>296</v>
       </c>
       <c r="I126" t="n">
-        <v>29.99</v>
+        <v>29990</v>
       </c>
       <c r="J126" t="n">
-        <v>3.8987</v>
+        <v>3898.7</v>
       </c>
     </row>
     <row r="127">
@@ -6099,10 +6099,10 @@
         <v>298</v>
       </c>
       <c r="I127" t="n">
-        <v>69.98</v>
+        <v>69980</v>
       </c>
       <c r="J127" t="n">
-        <v>9.0974</v>
+        <v>9097.4</v>
       </c>
     </row>
     <row r="128">
@@ -6131,10 +6131,10 @@
         <v>300</v>
       </c>
       <c r="I128" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J128" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="129">
@@ -6163,10 +6163,10 @@
         <v>302</v>
       </c>
       <c r="I129" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J129" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="130">
@@ -6195,10 +6195,10 @@
         <v>304</v>
       </c>
       <c r="I130" t="n">
-        <v>139.99</v>
+        <v>139990</v>
       </c>
       <c r="J130" t="n">
-        <v>18.1987</v>
+        <v>18198.7</v>
       </c>
     </row>
     <row r="131">
@@ -6227,10 +6227,10 @@
         <v>307</v>
       </c>
       <c r="I131" t="n">
-        <v>379.98</v>
+        <v>379980</v>
       </c>
       <c r="J131" t="n">
-        <v>49.3974</v>
+        <v>49397.4</v>
       </c>
     </row>
     <row r="132">
@@ -6259,10 +6259,10 @@
         <v>309</v>
       </c>
       <c r="I132" t="n">
-        <v>189.99</v>
+        <v>189990</v>
       </c>
       <c r="J132" t="n">
-        <v>24.6987</v>
+        <v>24698.7</v>
       </c>
     </row>
     <row r="133">
@@ -6291,10 +6291,10 @@
         <v>311</v>
       </c>
       <c r="I133" t="n">
-        <v>249.99</v>
+        <v>249990</v>
       </c>
       <c r="J133" t="n">
-        <v>32.4987</v>
+        <v>32498.7</v>
       </c>
     </row>
     <row r="134">
@@ -6323,10 +6323,10 @@
         <v>313</v>
       </c>
       <c r="I134" t="n">
-        <v>299.99</v>
+        <v>299990</v>
       </c>
       <c r="J134" t="n">
-        <v>38.9987</v>
+        <v>38998.7</v>
       </c>
     </row>
     <row r="135">
@@ -6355,10 +6355,10 @@
         <v>315</v>
       </c>
       <c r="I135" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J135" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="136">
@@ -6387,10 +6387,10 @@
         <v>317</v>
       </c>
       <c r="I136" t="n">
-        <v>199.97</v>
+        <v>199970</v>
       </c>
       <c r="J136" t="n">
-        <v>25.9961</v>
+        <v>25996.1</v>
       </c>
     </row>
     <row r="137">
@@ -6419,10 +6419,10 @@
         <v>319</v>
       </c>
       <c r="I137" t="n">
-        <v>165.99</v>
+        <v>165990</v>
       </c>
       <c r="J137" t="n">
-        <v>21.5787</v>
+        <v>21578.7</v>
       </c>
     </row>
     <row r="138">
@@ -6451,10 +6451,10 @@
         <v>321</v>
       </c>
       <c r="I138" t="n">
-        <v>194.985</v>
+        <v>194985</v>
       </c>
       <c r="J138" t="n">
-        <v>25.34805</v>
+        <v>25348.05</v>
       </c>
     </row>
     <row r="139">
@@ -6483,10 +6483,10 @@
         <v>324</v>
       </c>
       <c r="I139" t="n">
-        <v>329.96</v>
+        <v>329960</v>
       </c>
       <c r="J139" t="n">
-        <v>42.8948</v>
+        <v>42894.8</v>
       </c>
     </row>
     <row r="140">
@@ -6515,10 +6515,10 @@
         <v>326</v>
       </c>
       <c r="I140" t="n">
-        <v>64.995</v>
+        <v>64995</v>
       </c>
       <c r="J140" t="n">
-        <v>8.44935</v>
+        <v>8449.35</v>
       </c>
     </row>
     <row r="141">
@@ -6547,10 +6547,10 @@
         <v>329</v>
       </c>
       <c r="I141" t="n">
-        <v>21.99</v>
+        <v>21990</v>
       </c>
       <c r="J141" t="n">
-        <v>2.8587</v>
+        <v>2858.7</v>
       </c>
     </row>
     <row r="142">
@@ -6579,10 +6579,10 @@
         <v>331</v>
       </c>
       <c r="I142" t="n">
-        <v>167.96</v>
+        <v>167960</v>
       </c>
       <c r="J142" t="n">
-        <v>21.8348</v>
+        <v>21834.8</v>
       </c>
     </row>
     <row r="143">
@@ -6611,10 +6611,10 @@
         <v>333</v>
       </c>
       <c r="I143" t="n">
-        <v>359.982</v>
+        <v>359982</v>
       </c>
       <c r="J143" t="n">
-        <v>46.79766</v>
+        <v>46797.66</v>
       </c>
     </row>
     <row r="144">
@@ -6643,10 +6643,10 @@
         <v>335</v>
       </c>
       <c r="I144" t="n">
-        <v>129.97</v>
+        <v>129970</v>
       </c>
       <c r="J144" t="n">
-        <v>16.8961</v>
+        <v>16896.1</v>
       </c>
     </row>
     <row r="145">
@@ -6675,10 +6675,10 @@
         <v>337</v>
       </c>
       <c r="I145" t="n">
-        <v>55.99</v>
+        <v>55990</v>
       </c>
       <c r="J145" t="n">
-        <v>7.2787</v>
+        <v>7278.7</v>
       </c>
     </row>
     <row r="146">
@@ -6707,10 +6707,10 @@
         <v>339</v>
       </c>
       <c r="I146" t="n">
-        <v>199.99</v>
+        <v>199990</v>
       </c>
       <c r="J146" t="n">
-        <v>25.9987</v>
+        <v>25998.7</v>
       </c>
     </row>
     <row r="147">
@@ -6739,10 +6739,10 @@
         <v>341</v>
       </c>
       <c r="I147" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J147" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="148">
@@ -6771,10 +6771,10 @@
         <v>341</v>
       </c>
       <c r="I148" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J148" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="149">
@@ -6803,10 +6803,10 @@
         <v>345</v>
       </c>
       <c r="I149" t="n">
-        <v>74.98</v>
+        <v>74980</v>
       </c>
       <c r="J149" t="n">
-        <v>9.7474</v>
+        <v>9747.4</v>
       </c>
     </row>
     <row r="150">
@@ -6835,10 +6835,10 @@
         <v>347</v>
       </c>
       <c r="I150" t="n">
-        <v>29.99</v>
+        <v>29990</v>
       </c>
       <c r="J150" t="n">
-        <v>3.8987</v>
+        <v>3898.7</v>
       </c>
     </row>
     <row r="151">
@@ -6867,10 +6867,10 @@
         <v>349</v>
       </c>
       <c r="I151" t="n">
-        <v>21.99</v>
+        <v>21990</v>
       </c>
       <c r="J151" t="n">
-        <v>2.8587</v>
+        <v>2858.7</v>
       </c>
     </row>
     <row r="152">
@@ -6899,10 +6899,10 @@
         <v>351</v>
       </c>
       <c r="I152" t="n">
-        <v>192.96</v>
+        <v>192960</v>
       </c>
       <c r="J152" t="n">
-        <v>25.0848</v>
+        <v>25084.8</v>
       </c>
     </row>
     <row r="153">
@@ -6931,10 +6931,10 @@
         <v>354</v>
       </c>
       <c r="I153" t="n">
-        <v>24.99</v>
+        <v>24990</v>
       </c>
       <c r="J153" t="n">
-        <v>3.2487</v>
+        <v>3248.7</v>
       </c>
     </row>
     <row r="154">
@@ -6963,10 +6963,10 @@
         <v>356</v>
       </c>
       <c r="I154" t="n">
-        <v>676.85</v>
+        <v>676850</v>
       </c>
       <c r="J154" t="n">
-        <v>94.759</v>
+        <v>94759</v>
       </c>
     </row>
     <row r="155">
@@ -6995,10 +6995,10 @@
         <v>358</v>
       </c>
       <c r="I155" t="n">
-        <v>226.98</v>
+        <v>226980</v>
       </c>
       <c r="J155" t="n">
-        <v>29.5074</v>
+        <v>29507.4</v>
       </c>
     </row>
     <row r="156">
@@ -7027,10 +7027,10 @@
         <v>360</v>
       </c>
       <c r="I156" t="n">
-        <v>501.955</v>
+        <v>501955</v>
       </c>
       <c r="J156" t="n">
-        <v>70.2737</v>
+        <v>70273.7</v>
       </c>
     </row>
     <row r="157">
@@ -7059,10 +7059,10 @@
         <v>362</v>
       </c>
       <c r="I157" t="n">
-        <v>29.99</v>
+        <v>29990</v>
       </c>
       <c r="J157" t="n">
-        <v>3.8987</v>
+        <v>3898.7</v>
       </c>
     </row>
     <row r="158">
@@ -7091,10 +7091,10 @@
         <v>364</v>
       </c>
       <c r="I158" t="n">
-        <v>199.99</v>
+        <v>199990</v>
       </c>
       <c r="J158" t="n">
-        <v>25.9987</v>
+        <v>25998.7</v>
       </c>
     </row>
     <row r="159">
@@ -7123,10 +7123,10 @@
         <v>366</v>
       </c>
       <c r="I159" t="n">
-        <v>361.755</v>
+        <v>361755</v>
       </c>
       <c r="J159" t="n">
-        <v>47.02815</v>
+        <v>47028.15</v>
       </c>
     </row>
     <row r="160">
@@ -7155,10 +7155,10 @@
         <v>368</v>
       </c>
       <c r="I160" t="n">
-        <v>299.99</v>
+        <v>299990</v>
       </c>
       <c r="J160" t="n">
-        <v>38.9987</v>
+        <v>38998.7</v>
       </c>
     </row>
     <row r="161">
@@ -7187,10 +7187,10 @@
         <v>370</v>
       </c>
       <c r="I161" t="n">
-        <v>49.99</v>
+        <v>49990</v>
       </c>
       <c r="J161" t="n">
-        <v>6.4987</v>
+        <v>6498.7</v>
       </c>
     </row>
     <row r="162">
@@ -7219,10 +7219,10 @@
         <v>373</v>
       </c>
       <c r="I162" t="n">
-        <v>84.99</v>
+        <v>84990</v>
       </c>
       <c r="J162" t="n">
-        <v>11.0487</v>
+        <v>11048.7</v>
       </c>
     </row>
     <row r="163">
@@ -7251,10 +7251,10 @@
         <v>375</v>
       </c>
       <c r="I163" t="n">
-        <v>132.96</v>
+        <v>132960</v>
       </c>
       <c r="J163" t="n">
-        <v>17.2848</v>
+        <v>17284.8</v>
       </c>
     </row>
     <row r="164">
@@ -7283,10 +7283,10 @@
         <v>377</v>
       </c>
       <c r="I164" t="n">
-        <v>359.67</v>
+        <v>359670</v>
       </c>
       <c r="J164" t="n">
-        <v>46.7571</v>
+        <v>46757.1</v>
       </c>
     </row>
     <row r="165">
@@ -7315,10 +7315,10 @@
         <v>379</v>
       </c>
       <c r="I165" t="n">
-        <v>469.94</v>
+        <v>469940</v>
       </c>
       <c r="J165" t="n">
-        <v>65.7916</v>
+        <v>65791.6</v>
       </c>
     </row>
     <row r="166">
@@ -7347,10 +7347,10 @@
         <v>381</v>
       </c>
       <c r="I166" t="n">
-        <v>648.92</v>
+        <v>648920</v>
       </c>
       <c r="J166" t="n">
-        <v>90.8488</v>
+        <v>90848.8</v>
       </c>
     </row>
     <row r="167">
@@ -7379,10 +7379,10 @@
         <v>383</v>
       </c>
       <c r="I167" t="n">
-        <v>249.99</v>
+        <v>249990</v>
       </c>
       <c r="J167" t="n">
-        <v>32.4987</v>
+        <v>32498.7</v>
       </c>
     </row>
     <row r="168">
@@ -7411,10 +7411,10 @@
         <v>385</v>
       </c>
       <c r="I168" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J168" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="169">
@@ -7443,10 +7443,10 @@
         <v>377</v>
       </c>
       <c r="I169" t="n">
-        <v>359.67</v>
+        <v>359670</v>
       </c>
       <c r="J169" t="n">
-        <v>46.7571</v>
+        <v>46757.1</v>
       </c>
     </row>
     <row r="170">
@@ -7475,10 +7475,10 @@
         <v>388</v>
       </c>
       <c r="I170" t="n">
-        <v>27.98</v>
+        <v>27980</v>
       </c>
       <c r="J170" t="n">
-        <v>3.6374</v>
+        <v>3637.4</v>
       </c>
     </row>
     <row r="171">
@@ -7507,10 +7507,10 @@
         <v>390</v>
       </c>
       <c r="I171" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J171" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="172">
@@ -7539,10 +7539,10 @@
         <v>392</v>
       </c>
       <c r="I172" t="n">
-        <v>67.94</v>
+        <v>67940</v>
       </c>
       <c r="J172" t="n">
-        <v>8.8322</v>
+        <v>8832.2</v>
       </c>
     </row>
     <row r="173">
@@ -7571,10 +7571,10 @@
         <v>394</v>
       </c>
       <c r="I173" t="n">
-        <v>264.97</v>
+        <v>264970</v>
       </c>
       <c r="J173" t="n">
-        <v>34.4461</v>
+        <v>34446.1</v>
       </c>
     </row>
     <row r="174">
@@ -7603,10 +7603,10 @@
         <v>396</v>
       </c>
       <c r="I174" t="n">
-        <v>139.95</v>
+        <v>139950</v>
       </c>
       <c r="J174" t="n">
-        <v>18.1935</v>
+        <v>18193.5</v>
       </c>
     </row>
     <row r="175">
@@ -7635,10 +7635,10 @@
         <v>398</v>
       </c>
       <c r="I175" t="n">
-        <v>12.99</v>
+        <v>12990</v>
       </c>
       <c r="J175" t="n">
-        <v>1.6887</v>
+        <v>1688.7</v>
       </c>
     </row>
     <row r="176">
@@ -7667,10 +7667,10 @@
         <v>400</v>
       </c>
       <c r="I176" t="n">
-        <v>254.985</v>
+        <v>254985</v>
       </c>
       <c r="J176" t="n">
-        <v>33.14805</v>
+        <v>33148.05</v>
       </c>
     </row>
     <row r="177">
@@ -7699,10 +7699,10 @@
         <v>402</v>
       </c>
       <c r="I177" t="n">
-        <v>229.99</v>
+        <v>229990</v>
       </c>
       <c r="J177" t="n">
-        <v>29.8987</v>
+        <v>29898.7</v>
       </c>
     </row>
     <row r="178">
@@ -7731,10 +7731,10 @@
         <v>404</v>
       </c>
       <c r="I178" t="n">
-        <v>154.96</v>
+        <v>154960</v>
       </c>
       <c r="J178" t="n">
-        <v>20.1448</v>
+        <v>20144.8</v>
       </c>
     </row>
     <row r="179">
@@ -7763,10 +7763,10 @@
         <v>406</v>
       </c>
       <c r="I179" t="n">
-        <v>214.96</v>
+        <v>214960</v>
       </c>
       <c r="J179" t="n">
-        <v>27.9448</v>
+        <v>27944.8</v>
       </c>
     </row>
     <row r="180">
@@ -7795,10 +7795,10 @@
         <v>408</v>
       </c>
       <c r="I180" t="n">
-        <v>50.97</v>
+        <v>50970</v>
       </c>
       <c r="J180" t="n">
-        <v>6.6261</v>
+        <v>6626.1</v>
       </c>
     </row>
     <row r="181">
@@ -7827,10 +7827,10 @@
         <v>410</v>
       </c>
       <c r="I181" t="n">
-        <v>479.98</v>
+        <v>479980</v>
       </c>
       <c r="J181" t="n">
-        <v>67.1972</v>
+        <v>67197.2</v>
       </c>
     </row>
     <row r="182">
@@ -7859,10 +7859,10 @@
         <v>412</v>
       </c>
       <c r="I182" t="n">
-        <v>199.99</v>
+        <v>199990</v>
       </c>
       <c r="J182" t="n">
-        <v>25.9987</v>
+        <v>25998.7</v>
       </c>
     </row>
     <row r="183">
@@ -7891,10 +7891,10 @@
         <v>414</v>
       </c>
       <c r="I183" t="n">
-        <v>79.99</v>
+        <v>79990</v>
       </c>
       <c r="J183" t="n">
-        <v>10.3987</v>
+        <v>10398.7</v>
       </c>
     </row>
     <row r="184">
@@ -7923,10 +7923,10 @@
         <v>416</v>
       </c>
       <c r="I184" t="n">
-        <v>279.99</v>
+        <v>279990</v>
       </c>
       <c r="J184" t="n">
-        <v>36.3987</v>
+        <v>36398.7</v>
       </c>
     </row>
     <row r="185">
@@ -7955,10 +7955,10 @@
         <v>418</v>
       </c>
       <c r="I185" t="n">
-        <v>229.99</v>
+        <v>229990</v>
       </c>
       <c r="J185" t="n">
-        <v>29.8987</v>
+        <v>29898.7</v>
       </c>
     </row>
     <row r="186">
@@ -7987,10 +7987,10 @@
         <v>421</v>
       </c>
       <c r="I186" t="n">
-        <v>223.97</v>
+        <v>223970</v>
       </c>
       <c r="J186" t="n">
-        <v>29.1161</v>
+        <v>29116.1</v>
       </c>
     </row>
     <row r="187">
@@ -8019,10 +8019,10 @@
         <v>423</v>
       </c>
       <c r="I187" t="n">
-        <v>79.97</v>
+        <v>79970</v>
       </c>
       <c r="J187" t="n">
-        <v>10.3961</v>
+        <v>10396.1</v>
       </c>
     </row>
     <row r="188">
@@ -8051,10 +8051,10 @@
         <v>425</v>
       </c>
       <c r="I188" t="n">
-        <v>279.97</v>
+        <v>279970</v>
       </c>
       <c r="J188" t="n">
-        <v>36.3961</v>
+        <v>36396.1</v>
       </c>
     </row>
     <row r="189">
@@ -8083,10 +8083,10 @@
         <v>427</v>
       </c>
       <c r="I189" t="n">
-        <v>74.98</v>
+        <v>74980</v>
       </c>
       <c r="J189" t="n">
-        <v>9.7474</v>
+        <v>9747.4</v>
       </c>
     </row>
     <row r="190">
@@ -8115,10 +8115,10 @@
         <v>429</v>
       </c>
       <c r="I190" t="n">
-        <v>189.99</v>
+        <v>189990</v>
       </c>
       <c r="J190" t="n">
-        <v>24.6987</v>
+        <v>24698.7</v>
       </c>
     </row>
     <row r="191">
@@ -8147,10 +8147,10 @@
         <v>431</v>
       </c>
       <c r="I191" t="n">
-        <v>124.97</v>
+        <v>124970</v>
       </c>
       <c r="J191" t="n">
-        <v>16.2461</v>
+        <v>16246.1</v>
       </c>
     </row>
     <row r="192">
@@ -8179,10 +8179,10 @@
         <v>433</v>
       </c>
       <c r="I192" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J192" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="193">
@@ -8211,10 +8211,10 @@
         <v>435</v>
       </c>
       <c r="I193" t="n">
-        <v>49.99</v>
+        <v>49990</v>
       </c>
       <c r="J193" t="n">
-        <v>6.4987</v>
+        <v>6498.7</v>
       </c>
     </row>
     <row r="194">
@@ -8243,10 +8243,10 @@
         <v>437</v>
       </c>
       <c r="I194" t="n">
-        <v>164.99</v>
+        <v>164990</v>
       </c>
       <c r="J194" t="n">
-        <v>21.4487</v>
+        <v>21448.7</v>
       </c>
     </row>
     <row r="195">
@@ -8275,10 +8275,10 @@
         <v>439</v>
       </c>
       <c r="I195" t="n">
-        <v>559.98</v>
+        <v>559980</v>
       </c>
       <c r="J195" t="n">
-        <v>78.3972</v>
+        <v>78397.2</v>
       </c>
     </row>
     <row r="196">
@@ -8307,10 +8307,10 @@
         <v>442</v>
       </c>
       <c r="I196" t="n">
-        <v>179.98</v>
+        <v>179980</v>
       </c>
       <c r="J196" t="n">
-        <v>23.3974</v>
+        <v>23397.4</v>
       </c>
     </row>
     <row r="197">
@@ -8339,10 +8339,10 @@
         <v>444</v>
       </c>
       <c r="I197" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J197" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="198">
@@ -8371,10 +8371,10 @@
         <v>446</v>
       </c>
       <c r="I198" t="n">
-        <v>59.99</v>
+        <v>59990</v>
       </c>
       <c r="J198" t="n">
-        <v>7.7987</v>
+        <v>7798.7</v>
       </c>
     </row>
     <row r="199">
@@ -8403,10 +8403,10 @@
         <v>448</v>
       </c>
       <c r="I199" t="n">
-        <v>69.99</v>
+        <v>69990</v>
       </c>
       <c r="J199" t="n">
-        <v>9.0987</v>
+        <v>9098.7</v>
       </c>
     </row>
     <row r="200">
@@ -8435,10 +8435,10 @@
         <v>450</v>
       </c>
       <c r="I200" t="n">
-        <v>219.99</v>
+        <v>219990</v>
       </c>
       <c r="J200" t="n">
-        <v>28.5987</v>
+        <v>28598.7</v>
       </c>
     </row>
     <row r="201">
@@ -8467,10 +8467,10 @@
         <v>452</v>
       </c>
       <c r="I201" t="n">
-        <v>333.95</v>
+        <v>333950</v>
       </c>
       <c r="J201" t="n">
-        <v>43.4135</v>
+        <v>43413.5</v>
       </c>
     </row>
     <row r="202">
@@ -8499,10 +8499,10 @@
         <v>454</v>
       </c>
       <c r="I202" t="n">
-        <v>169.99</v>
+        <v>169990</v>
       </c>
       <c r="J202" t="n">
-        <v>22.0987</v>
+        <v>22098.7</v>
       </c>
     </row>
     <row r="203">
@@ -8531,10 +8531,10 @@
         <v>456</v>
       </c>
       <c r="I203" t="n">
-        <v>239.98</v>
+        <v>239980</v>
       </c>
       <c r="J203" t="n">
-        <v>31.1974</v>
+        <v>31197.4</v>
       </c>
     </row>
     <row r="204">
@@ -8563,10 +8563,10 @@
         <v>458</v>
       </c>
       <c r="I204" t="n">
-        <v>29.99</v>
+        <v>29990</v>
       </c>
       <c r="J204" t="n">
-        <v>3.8987</v>
+        <v>3898.7</v>
       </c>
     </row>
     <row r="205">
@@ -8595,10 +8595,10 @@
         <v>460</v>
       </c>
       <c r="I205" t="n">
-        <v>259.99</v>
+        <v>259990</v>
       </c>
       <c r="J205" t="n">
-        <v>33.7987</v>
+        <v>33798.7</v>
       </c>
     </row>
     <row r="206">
@@ -8627,10 +8627,10 @@
         <v>463</v>
       </c>
       <c r="I206" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J206" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="207">
@@ -8659,10 +8659,10 @@
         <v>465</v>
       </c>
       <c r="I207" t="n">
-        <v>189.99</v>
+        <v>189990</v>
       </c>
       <c r="J207" t="n">
-        <v>24.6987</v>
+        <v>24698.7</v>
       </c>
     </row>
     <row r="208">
@@ -8691,10 +8691,10 @@
         <v>467</v>
       </c>
       <c r="I208" t="n">
-        <v>49.99</v>
+        <v>49990</v>
       </c>
       <c r="J208" t="n">
-        <v>6.4987</v>
+        <v>6498.7</v>
       </c>
     </row>
     <row r="209">
@@ -8723,10 +8723,10 @@
         <v>469</v>
       </c>
       <c r="I209" t="n">
-        <v>49.99</v>
+        <v>49990</v>
       </c>
       <c r="J209" t="n">
-        <v>6.4987</v>
+        <v>6498.7</v>
       </c>
     </row>
     <row r="210">
@@ -8755,10 +8755,10 @@
         <v>471</v>
       </c>
       <c r="I210" t="n">
-        <v>199.99</v>
+        <v>199990</v>
       </c>
       <c r="J210" t="n">
-        <v>25.9987</v>
+        <v>25998.7</v>
       </c>
     </row>
     <row r="211">
@@ -8787,10 +8787,10 @@
         <v>473</v>
       </c>
       <c r="I211" t="n">
-        <v>189.99</v>
+        <v>189990</v>
       </c>
       <c r="J211" t="n">
-        <v>24.6987</v>
+        <v>24698.7</v>
       </c>
     </row>
     <row r="212">
@@ -8819,10 +8819,10 @@
         <v>475</v>
       </c>
       <c r="I212" t="n">
-        <v>219.98</v>
+        <v>219980</v>
       </c>
       <c r="J212" t="n">
-        <v>28.5974</v>
+        <v>28597.4</v>
       </c>
     </row>
     <row r="213">
@@ -8851,10 +8851,10 @@
         <v>477</v>
       </c>
       <c r="I213" t="n">
-        <v>189.99</v>
+        <v>189990</v>
       </c>
       <c r="J213" t="n">
-        <v>24.6987</v>
+        <v>24698.7</v>
       </c>
     </row>
     <row r="214">
@@ -8883,10 +8883,10 @@
         <v>479</v>
       </c>
       <c r="I214" t="n">
-        <v>91.96</v>
+        <v>91960</v>
       </c>
       <c r="J214" t="n">
-        <v>11.9548</v>
+        <v>11954.8</v>
       </c>
     </row>
     <row r="215">
@@ -8915,10 +8915,10 @@
         <v>482</v>
       </c>
       <c r="I215" t="n">
-        <v>229.99</v>
+        <v>229990</v>
       </c>
       <c r="J215" t="n">
-        <v>29.8987</v>
+        <v>29898.7</v>
       </c>
     </row>
     <row r="216">
@@ -8947,10 +8947,10 @@
         <v>485</v>
       </c>
       <c r="I216" t="n">
-        <v>229.99</v>
+        <v>229990</v>
       </c>
       <c r="J216" t="n">
-        <v>29.8987</v>
+        <v>29898.7</v>
       </c>
     </row>
     <row r="217">
@@ -8979,10 +8979,10 @@
         <v>487</v>
       </c>
       <c r="I217" t="n">
-        <v>92.98</v>
+        <v>92980</v>
       </c>
       <c r="J217" t="n">
-        <v>12.0874</v>
+        <v>12087.4</v>
       </c>
     </row>
     <row r="218">
@@ -9011,10 +9011,10 @@
         <v>490</v>
       </c>
       <c r="I218" t="n">
-        <v>152.97</v>
+        <v>152970</v>
       </c>
       <c r="J218" t="n">
-        <v>19.8861</v>
+        <v>19886.1</v>
       </c>
     </row>
     <row r="219">
@@ -9043,10 +9043,10 @@
         <v>492</v>
       </c>
       <c r="I219" t="n">
-        <v>42.98</v>
+        <v>42980</v>
       </c>
       <c r="J219" t="n">
-        <v>5.5874</v>
+        <v>5587.4</v>
       </c>
     </row>
     <row r="220">
@@ -9075,10 +9075,10 @@
         <v>494</v>
       </c>
       <c r="I220" t="n">
-        <v>230.98</v>
+        <v>230980</v>
       </c>
       <c r="J220" t="n">
-        <v>30.0274</v>
+        <v>30027.4</v>
       </c>
     </row>
     <row r="221">
@@ -9107,10 +9107,10 @@
         <v>496</v>
       </c>
       <c r="I221" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J221" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="222">
@@ -9139,10 +9139,10 @@
         <v>498</v>
       </c>
       <c r="I222" t="n">
-        <v>299.96</v>
+        <v>299960</v>
       </c>
       <c r="J222" t="n">
-        <v>38.9948</v>
+        <v>38994.8</v>
       </c>
     </row>
     <row r="223">
@@ -9171,10 +9171,10 @@
         <v>500</v>
       </c>
       <c r="I223" t="n">
-        <v>139.99</v>
+        <v>139990</v>
       </c>
       <c r="J223" t="n">
-        <v>18.1987</v>
+        <v>18198.7</v>
       </c>
     </row>
     <row r="224">
@@ -9203,10 +9203,10 @@
         <v>502</v>
       </c>
       <c r="I224" t="n">
-        <v>149.98</v>
+        <v>149980</v>
       </c>
       <c r="J224" t="n">
-        <v>19.4974</v>
+        <v>19497.4</v>
       </c>
     </row>
     <row r="225">
@@ -9235,10 +9235,10 @@
         <v>504</v>
       </c>
       <c r="I225" t="n">
-        <v>119.99</v>
+        <v>119990</v>
       </c>
       <c r="J225" t="n">
-        <v>15.5987</v>
+        <v>15598.7</v>
       </c>
     </row>
     <row r="226">
@@ -9267,10 +9267,10 @@
         <v>506</v>
       </c>
       <c r="I226" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J226" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="227">
@@ -9299,10 +9299,10 @@
         <v>508</v>
       </c>
       <c r="I227" t="n">
-        <v>29.99</v>
+        <v>29990</v>
       </c>
       <c r="J227" t="n">
-        <v>3.8987</v>
+        <v>3898.7</v>
       </c>
     </row>
     <row r="228">
@@ -9331,10 +9331,10 @@
         <v>510</v>
       </c>
       <c r="I228" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J228" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="229">
@@ -9363,10 +9363,10 @@
         <v>512</v>
       </c>
       <c r="I229" t="n">
-        <v>169.99</v>
+        <v>169990</v>
       </c>
       <c r="J229" t="n">
-        <v>22.0987</v>
+        <v>22098.7</v>
       </c>
     </row>
     <row r="230">
@@ -9395,10 +9395,10 @@
         <v>514</v>
       </c>
       <c r="I230" t="n">
-        <v>299.99</v>
+        <v>299990</v>
       </c>
       <c r="J230" t="n">
-        <v>38.9987</v>
+        <v>38998.7</v>
       </c>
     </row>
     <row r="231">
@@ -9427,10 +9427,10 @@
         <v>516</v>
       </c>
       <c r="I231" t="n">
-        <v>16.99</v>
+        <v>16990</v>
       </c>
       <c r="J231" t="n">
-        <v>2.2087</v>
+        <v>2208.7</v>
       </c>
     </row>
     <row r="232">
@@ -9459,10 +9459,10 @@
         <v>518</v>
       </c>
       <c r="I232" t="n">
-        <v>154.99</v>
+        <v>154990</v>
       </c>
       <c r="J232" t="n">
-        <v>20.1487</v>
+        <v>20148.7</v>
       </c>
     </row>
     <row r="233">
@@ -9491,10 +9491,10 @@
         <v>520</v>
       </c>
       <c r="I233" t="n">
-        <v>154.99</v>
+        <v>154990</v>
       </c>
       <c r="J233" t="n">
-        <v>20.1487</v>
+        <v>20148.7</v>
       </c>
     </row>
     <row r="234">
@@ -9523,10 +9523,10 @@
         <v>522</v>
       </c>
       <c r="I234" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J234" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="235">
@@ -9555,10 +9555,10 @@
         <v>524</v>
       </c>
       <c r="I235" t="n">
-        <v>39.99</v>
+        <v>39990</v>
       </c>
       <c r="J235" t="n">
-        <v>5.1987</v>
+        <v>5198.7</v>
       </c>
     </row>
     <row r="236">
@@ -9587,10 +9587,10 @@
         <v>526</v>
       </c>
       <c r="I236" t="n">
-        <v>99.97</v>
+        <v>99970</v>
       </c>
       <c r="J236" t="n">
-        <v>12.9961</v>
+        <v>12996.1</v>
       </c>
     </row>
     <row r="237">
@@ -9619,10 +9619,10 @@
         <v>528</v>
       </c>
       <c r="I237" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J237" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="238">
@@ -9651,10 +9651,10 @@
         <v>530</v>
       </c>
       <c r="I238" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J238" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="239">
@@ -9683,10 +9683,10 @@
         <v>532</v>
       </c>
       <c r="I239" t="n">
-        <v>167.94</v>
+        <v>167940</v>
       </c>
       <c r="J239" t="n">
-        <v>21.8322</v>
+        <v>21832.2</v>
       </c>
     </row>
     <row r="240">
@@ -9715,10 +9715,10 @@
         <v>534</v>
       </c>
       <c r="I240" t="n">
-        <v>141.98</v>
+        <v>141980</v>
       </c>
       <c r="J240" t="n">
-        <v>18.4574</v>
+        <v>18457.4</v>
       </c>
     </row>
     <row r="241">
@@ -9747,10 +9747,10 @@
         <v>536</v>
       </c>
       <c r="I241" t="n">
-        <v>84.99</v>
+        <v>84990</v>
       </c>
       <c r="J241" t="n">
-        <v>11.0487</v>
+        <v>11048.7</v>
       </c>
     </row>
     <row r="242">
@@ -9779,10 +9779,10 @@
         <v>538</v>
       </c>
       <c r="I242" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J242" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="243">
@@ -9811,10 +9811,10 @@
         <v>540</v>
       </c>
       <c r="I243" t="n">
-        <v>139.98</v>
+        <v>139980</v>
       </c>
       <c r="J243" t="n">
-        <v>18.1974</v>
+        <v>18197.4</v>
       </c>
     </row>
     <row r="244">
@@ -9843,10 +9843,10 @@
         <v>542</v>
       </c>
       <c r="I244" t="n">
-        <v>129.99</v>
+        <v>129990</v>
       </c>
       <c r="J244" t="n">
-        <v>16.8987</v>
+        <v>16898.7</v>
       </c>
     </row>
     <row r="245">
@@ -9875,10 +9875,10 @@
         <v>544</v>
       </c>
       <c r="I245" t="n">
-        <v>79.99</v>
+        <v>79990</v>
       </c>
       <c r="J245" t="n">
-        <v>10.3987</v>
+        <v>10398.7</v>
       </c>
     </row>
     <row r="246">
@@ -9907,10 +9907,10 @@
         <v>546</v>
       </c>
       <c r="I246" t="n">
-        <v>39.99</v>
+        <v>39990</v>
       </c>
       <c r="J246" t="n">
-        <v>5.1987</v>
+        <v>5198.7</v>
       </c>
     </row>
     <row r="247">
@@ -9939,10 +9939,10 @@
         <v>548</v>
       </c>
       <c r="I247" t="n">
-        <v>21.99</v>
+        <v>21990</v>
       </c>
       <c r="J247" t="n">
-        <v>2.8587</v>
+        <v>2858.7</v>
       </c>
     </row>
     <row r="248">
@@ -9971,10 +9971,10 @@
         <v>550</v>
       </c>
       <c r="I248" t="n">
-        <v>99.99</v>
+        <v>99990</v>
       </c>
       <c r="J248" t="n">
-        <v>12.9987</v>
+        <v>12998.7</v>
       </c>
     </row>
     <row r="249">
@@ -10003,10 +10003,10 @@
         <v>552</v>
       </c>
       <c r="I249" t="n">
-        <v>139.99</v>
+        <v>139990</v>
       </c>
       <c r="J249" t="n">
-        <v>18.1987</v>
+        <v>18198.7</v>
       </c>
     </row>
     <row r="250">
@@ -10035,10 +10035,10 @@
         <v>554</v>
       </c>
       <c r="I250" t="n">
-        <v>269.99</v>
+        <v>269990</v>
       </c>
       <c r="J250" t="n">
-        <v>35.0987</v>
+        <v>35098.7</v>
       </c>
     </row>
     <row r="251">
@@ -10067,10 +10067,10 @@
         <v>556</v>
       </c>
       <c r="I251" t="n">
-        <v>169.99</v>
+        <v>169990</v>
       </c>
       <c r="J251" t="n">
-        <v>22.0987</v>
+        <v>22098.7</v>
       </c>
     </row>
     <row r="252">
@@ -10099,10 +10099,10 @@
         <v>558</v>
       </c>
       <c r="I252" t="n">
-        <v>299.99</v>
+        <v>299990</v>
       </c>
       <c r="J252" t="n">
-        <v>38.9987</v>
+        <v>38998.7</v>
       </c>
     </row>
     <row r="253">
@@ -10131,10 +10131,10 @@
         <v>560</v>
       </c>
       <c r="I253" t="n">
-        <v>199.99</v>
+        <v>199990</v>
       </c>
       <c r="J253" t="n">
-        <v>25.9987</v>
+        <v>25998.7</v>
       </c>
     </row>
     <row r="254">
@@ -10163,10 +10163,10 @@
         <v>562</v>
       </c>
       <c r="I254" t="n">
-        <v>21.99</v>
+        <v>21990</v>
       </c>
       <c r="J254" t="n">
-        <v>2.8587</v>
+        <v>2858.7</v>
       </c>
     </row>
     <row r="255">
@@ -10195,10 +10195,10 @@
         <v>564</v>
       </c>
       <c r="I255" t="n">
-        <v>259.98</v>
+        <v>259980</v>
       </c>
       <c r="J255" t="n">
-        <v>33.7974</v>
+        <v>33797.4</v>
       </c>
     </row>
   </sheetData>
